--- a/resources/templates/standard/B2100-01.xlsx
+++ b/resources/templates/standard/B2100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>발행부서</t>
   </si>
@@ -716,7 +719,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -733,30 +738,30 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -767,7 +772,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -833,7 +838,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -851,7 +856,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -871,7 +876,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -889,7 +894,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -909,7 +914,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -945,7 +950,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1138,7 +1143,7 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -1153,7 +1158,7 @@
     </row>
     <row r="13" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1176,7 +1181,7 @@
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W13" s="9"/>
       <c r="X13" s="9"/>
@@ -1212,7 +1217,7 @@
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W14" s="17"/>
       <c r="X14" s="17"/>
@@ -1227,7 +1232,7 @@
     </row>
     <row r="15" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1245,37 +1250,37 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
     </row>
     <row r="16" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -1345,7 +1350,7 @@
     </row>
     <row r="18" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1517,7 +1522,7 @@
     </row>
     <row r="23" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -1689,7 +1694,7 @@
     </row>
     <row r="28" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -1707,7 +1712,7 @@
       <c r="O28" s="23"/>
       <c r="P28" s="24"/>
       <c r="Q28" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
@@ -1795,7 +1800,7 @@
     </row>
     <row r="31" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -1820,7 +1825,7 @@
       <c r="V31" s="21"/>
       <c r="W31" s="21"/>
       <c r="X31" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
@@ -1856,17 +1861,17 @@
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
       <c r="AA32" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
       <c r="AD32" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE32" s="9"/>
       <c r="AF32" s="9"/>
@@ -1964,17 +1969,17 @@
       <c r="V35" s="13"/>
       <c r="W35" s="13"/>
       <c r="X35" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y35" s="18"/>
       <c r="Z35" s="18"/>
       <c r="AA35" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB35" s="18"/>
       <c r="AC35" s="18"/>
       <c r="AD35" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE35" s="18"/>
       <c r="AF35" s="18"/>
